--- a/output/graficos_otras_relaciones/plot_comunal_d_otrasrel_a_2022_maule.xlsx
+++ b/output/graficos_otras_relaciones/plot_comunal_d_otrasrel_a_2022_maule.xlsx
@@ -398,22 +398,22 @@
         </is>
       </c>
       <c r="B2">
+        <v>28.19869577238733</v>
+      </c>
+      <c r="C2">
         <v>32.34808176037009</v>
-      </c>
-      <c r="C2">
-        <v>28.19869577238733</v>
       </c>
       <c r="D2">
         <v>3.091373415610407</v>
       </c>
       <c r="E2">
-        <v>20.14869576175074</v>
+        <v>17.56416180115092</v>
       </c>
       <c r="F2">
         <v>62.28714243709833</v>
       </c>
       <c r="G2">
-        <v>17.56416180115092</v>
+        <v>20.14869576175074</v>
       </c>
     </row>
     <row r="3">
@@ -423,22 +423,22 @@
         </is>
       </c>
       <c r="B3">
+        <v>29.37332847070265</v>
+      </c>
+      <c r="C3">
         <v>29.37636761487965</v>
-      </c>
-      <c r="C3">
-        <v>29.37332847070265</v>
       </c>
       <c r="D3">
         <v>3.404096834264432</v>
       </c>
       <c r="E3">
-        <v>18.50483392361443</v>
+        <v>18.5029194984206</v>
       </c>
       <c r="F3">
         <v>62.99224657796496</v>
       </c>
       <c r="G3">
-        <v>18.5029194984206</v>
+        <v>18.50483392361443</v>
       </c>
     </row>
     <row r="4">
@@ -448,22 +448,22 @@
         </is>
       </c>
       <c r="B4">
+        <v>25.12085347557926</v>
+      </c>
+      <c r="C4">
         <v>54.29238206367728</v>
-      </c>
-      <c r="C4">
-        <v>25.12085347557926</v>
       </c>
       <c r="D4">
         <v>1.841879029782008</v>
       </c>
       <c r="E4">
-        <v>30.26107962463997</v>
+        <v>14.00167239617207</v>
       </c>
       <c r="F4">
         <v>55.73724797918796</v>
       </c>
       <c r="G4">
-        <v>14.00167239617207</v>
+        <v>30.26107962463997</v>
       </c>
     </row>
     <row r="5">
@@ -473,22 +473,22 @@
         </is>
       </c>
       <c r="B5">
+        <v>32.3943661971831</v>
+      </c>
+      <c r="C5">
         <v>37.55868544600939</v>
-      </c>
-      <c r="C5">
-        <v>32.3943661971831</v>
       </c>
       <c r="D5">
         <v>2.6625</v>
       </c>
       <c r="E5">
-        <v>22.09944751381215</v>
+        <v>19.06077348066298</v>
       </c>
       <c r="F5">
         <v>58.83977900552485</v>
       </c>
       <c r="G5">
-        <v>19.06077348066298</v>
+        <v>22.09944751381215</v>
       </c>
     </row>
     <row r="6">
@@ -498,22 +498,22 @@
         </is>
       </c>
       <c r="B6">
+        <v>34.63377205925751</v>
+      </c>
+      <c r="C6">
         <v>19.77807944283775</v>
-      </c>
-      <c r="C6">
-        <v>34.63377205925751</v>
       </c>
       <c r="D6">
         <v>5.056102655923605</v>
       </c>
       <c r="E6">
-        <v>12.80865377264735</v>
+        <v>22.42947786866447</v>
       </c>
       <c r="F6">
         <v>64.76186835868818</v>
       </c>
       <c r="G6">
-        <v>22.42947786866447</v>
+        <v>12.80865377264735</v>
       </c>
     </row>
     <row r="7">
@@ -523,22 +523,22 @@
         </is>
       </c>
       <c r="B7">
+        <v>28.20549108406453</v>
+      </c>
+      <c r="C7">
         <v>37.85734503255024</v>
-      </c>
-      <c r="C7">
-        <v>28.20549108406453</v>
       </c>
       <c r="D7">
         <v>2.641495327102804</v>
       </c>
       <c r="E7">
-        <v>22.79700017044486</v>
+        <v>16.98483040736322</v>
       </c>
       <c r="F7">
         <v>60.21816942219191</v>
       </c>
       <c r="G7">
-        <v>16.98483040736322</v>
+        <v>22.79700017044486</v>
       </c>
     </row>
     <row r="8">
@@ -548,22 +548,22 @@
         </is>
       </c>
       <c r="B8">
+        <v>22.62140356218602</v>
+      </c>
+      <c r="C8">
         <v>38.77302481351804</v>
-      </c>
-      <c r="C8">
-        <v>22.62140356218602</v>
       </c>
       <c r="D8">
         <v>2.57911268158618</v>
       </c>
       <c r="E8">
-        <v>24.02376910016978</v>
+        <v>14.01622335408413</v>
       </c>
       <c r="F8">
         <v>61.96000754574608</v>
       </c>
       <c r="G8">
-        <v>14.01622335408413</v>
+        <v>24.02376910016978</v>
       </c>
     </row>
     <row r="9">
@@ -573,22 +573,22 @@
         </is>
       </c>
       <c r="B9">
+        <v>28.26808896045084</v>
+      </c>
+      <c r="C9">
         <v>36.31880849350911</v>
-      </c>
-      <c r="C9">
-        <v>28.26808896045084</v>
       </c>
       <c r="D9">
         <v>2.753394292047659</v>
       </c>
       <c r="E9">
-        <v>22.06664628553959</v>
+        <v>17.17517578722104</v>
       </c>
       <c r="F9">
         <v>60.75817792723939</v>
       </c>
       <c r="G9">
-        <v>17.17517578722104</v>
+        <v>22.06664628553959</v>
       </c>
     </row>
     <row r="10">
@@ -598,22 +598,22 @@
         </is>
       </c>
       <c r="B10">
+        <v>30.4721606555175</v>
+      </c>
+      <c r="C10">
         <v>34.4113103633555</v>
-      </c>
-      <c r="C10">
-        <v>30.4721606555175</v>
       </c>
       <c r="D10">
         <v>2.906021274519372</v>
       </c>
       <c r="E10">
-        <v>20.87007882034258</v>
+        <v>18.48102812684576</v>
       </c>
       <c r="F10">
         <v>60.64889305281167</v>
       </c>
       <c r="G10">
-        <v>18.48102812684576</v>
+        <v>20.87007882034258</v>
       </c>
     </row>
     <row r="11">
@@ -623,22 +623,22 @@
         </is>
       </c>
       <c r="B11">
+        <v>26.91458026509573</v>
+      </c>
+      <c r="C11">
         <v>32.86696121747668</v>
-      </c>
-      <c r="C11">
-        <v>26.91458026509573</v>
       </c>
       <c r="D11">
         <v>3.042569081404033</v>
       </c>
       <c r="E11">
-        <v>20.56993624702358</v>
+        <v>16.84461172133036</v>
       </c>
       <c r="F11">
         <v>62.58545203164606</v>
       </c>
       <c r="G11">
-        <v>16.84461172133036</v>
+        <v>20.56993624702358</v>
       </c>
     </row>
     <row r="12">
@@ -648,22 +648,22 @@
         </is>
       </c>
       <c r="B12">
+        <v>29.86894462088855</v>
+      </c>
+      <c r="C12">
         <v>41.88661336837878</v>
-      </c>
-      <c r="C12">
-        <v>29.86894462088855</v>
       </c>
       <c r="D12">
         <v>2.387397594561618</v>
       </c>
       <c r="E12">
-        <v>24.38734085740398</v>
+        <v>17.39038024187549</v>
       </c>
       <c r="F12">
         <v>58.22227890072052</v>
       </c>
       <c r="G12">
-        <v>17.39038024187549</v>
+        <v>24.38734085740398</v>
       </c>
     </row>
     <row r="13">
@@ -673,22 +673,22 @@
         </is>
       </c>
       <c r="B13">
+        <v>29.01157613535173</v>
+      </c>
+      <c r="C13">
         <v>43.79341050756901</v>
-      </c>
-      <c r="C13">
-        <v>29.01157613535173</v>
       </c>
       <c r="D13">
         <v>2.283448556323709</v>
       </c>
       <c r="E13">
-        <v>25.34267752241575</v>
+        <v>16.78862207564671</v>
       </c>
       <c r="F13">
         <v>57.86870040193755</v>
       </c>
       <c r="G13">
-        <v>16.78862207564671</v>
+        <v>25.34267752241575</v>
       </c>
     </row>
     <row r="14">
@@ -698,22 +698,22 @@
         </is>
       </c>
       <c r="B14">
+        <v>26.12540192926045</v>
+      </c>
+      <c r="C14">
         <v>40.12861736334405</v>
-      </c>
-      <c r="C14">
-        <v>26.12540192926045</v>
       </c>
       <c r="D14">
         <v>2.491987179487179</v>
       </c>
       <c r="E14">
-        <v>24.1369306643458</v>
+        <v>15.71414756793347</v>
       </c>
       <c r="F14">
-        <v>60.14892176772072</v>
+        <v>60.14892176772073</v>
       </c>
       <c r="G14">
-        <v>15.71414756793347</v>
+        <v>24.13693066434581</v>
       </c>
     </row>
     <row r="15">
@@ -723,22 +723,22 @@
         </is>
       </c>
       <c r="B15">
+        <v>28.50236605524205</v>
+      </c>
+      <c r="C15">
         <v>29.27493654881325</v>
-      </c>
-      <c r="C15">
-        <v>28.50236605524205</v>
       </c>
       <c r="D15">
         <v>3.415891263615866</v>
       </c>
       <c r="E15">
-        <v>18.55459312945613</v>
+        <v>18.0649342996877</v>
       </c>
       <c r="F15">
         <v>63.38047257085616</v>
       </c>
       <c r="G15">
-        <v>18.0649342996877</v>
+        <v>18.55459312945613</v>
       </c>
     </row>
     <row r="16">
@@ -748,22 +748,22 @@
         </is>
       </c>
       <c r="B16">
+        <v>25.25557955363571</v>
+      </c>
+      <c r="C16">
         <v>43.02375809935205</v>
-      </c>
-      <c r="C16">
-        <v>25.25557955363571</v>
       </c>
       <c r="D16">
         <v>2.32429718875502</v>
       </c>
       <c r="E16">
-        <v>25.56686917087362</v>
+        <v>15.00812868999743</v>
       </c>
       <c r="F16">
         <v>59.42500213912895</v>
       </c>
       <c r="G16">
-        <v>15.00812868999743</v>
+        <v>25.56686917087362</v>
       </c>
     </row>
     <row r="17">
@@ -773,22 +773,22 @@
         </is>
       </c>
       <c r="B17">
+        <v>26.23674911660778</v>
+      </c>
+      <c r="C17">
         <v>40.15017667844523</v>
-      </c>
-      <c r="C17">
-        <v>26.23674911660778</v>
       </c>
       <c r="D17">
         <v>2.490649064906491</v>
       </c>
       <c r="E17">
-        <v>24.13060791080435</v>
+        <v>15.76851606052562</v>
       </c>
       <c r="F17">
         <v>60.10087602867003</v>
       </c>
       <c r="G17">
-        <v>15.76851606052562</v>
+        <v>24.13060791080435</v>
       </c>
     </row>
     <row r="18">
@@ -798,22 +798,22 @@
         </is>
       </c>
       <c r="B18">
+        <v>29.91427919559336</v>
+      </c>
+      <c r="C18">
         <v>34.08950164596982</v>
-      </c>
-      <c r="C18">
-        <v>29.91427919559336</v>
       </c>
       <c r="D18">
         <v>2.933454441151162</v>
       </c>
       <c r="E18">
-        <v>20.78580229738861</v>
+        <v>18.23999364044676</v>
       </c>
       <c r="F18">
         <v>60.97420406216463</v>
       </c>
       <c r="G18">
-        <v>18.23999364044676</v>
+        <v>20.78580229738861</v>
       </c>
     </row>
     <row r="19">
@@ -823,22 +823,22 @@
         </is>
       </c>
       <c r="B19">
+        <v>29.30522565320665</v>
+      </c>
+      <c r="C19">
         <v>37.90083135391924</v>
-      </c>
-      <c r="C19">
-        <v>29.30522565320665</v>
       </c>
       <c r="D19">
         <v>2.63846455150803</v>
       </c>
       <c r="E19">
-        <v>22.66714019355411</v>
+        <v>17.52641392169049</v>
       </c>
       <c r="F19">
         <v>59.80644588475539</v>
       </c>
       <c r="G19">
-        <v>17.52641392169049</v>
+        <v>22.66714019355411</v>
       </c>
     </row>
     <row r="20">
@@ -848,22 +848,22 @@
         </is>
       </c>
       <c r="B20">
+        <v>26.70477417277192</v>
+      </c>
+      <c r="C20">
         <v>30.27936559053216</v>
-      </c>
-      <c r="C20">
-        <v>26.70477417277192</v>
       </c>
       <c r="D20">
         <v>3.302579101302845</v>
       </c>
       <c r="E20">
-        <v>19.288168624032</v>
+        <v>17.01112877583466</v>
       </c>
       <c r="F20">
         <v>63.70070260013334</v>
       </c>
       <c r="G20">
-        <v>17.01112877583466</v>
+        <v>19.288168624032</v>
       </c>
     </row>
     <row r="21">
@@ -873,22 +873,22 @@
         </is>
       </c>
       <c r="B21">
+        <v>26.1610268378063</v>
+      </c>
+      <c r="C21">
         <v>34.63243873978997</v>
-      </c>
-      <c r="C21">
-        <v>26.1610268378063</v>
       </c>
       <c r="D21">
         <v>2.887466307277628</v>
       </c>
       <c r="E21">
-        <v>21.53846153846154</v>
+        <v>16.2699564586357</v>
       </c>
       <c r="F21">
         <v>62.19158200290276</v>
       </c>
       <c r="G21">
-        <v>16.2699564586357</v>
+        <v>21.53846153846154</v>
       </c>
     </row>
     <row r="22">
@@ -898,22 +898,22 @@
         </is>
       </c>
       <c r="B22">
+        <v>28.50126660807527</v>
+      </c>
+      <c r="C22">
         <v>34.94287339089076</v>
-      </c>
-      <c r="C22">
-        <v>28.50126660807527</v>
       </c>
       <c r="D22">
         <v>2.861813877792573</v>
       </c>
       <c r="E22">
-        <v>21.37909220306816</v>
+        <v>17.43792503558438</v>
       </c>
       <c r="F22">
         <v>61.18298276134747</v>
       </c>
       <c r="G22">
-        <v>17.43792503558438</v>
+        <v>21.37909220306816</v>
       </c>
     </row>
     <row r="23">
@@ -923,22 +923,22 @@
         </is>
       </c>
       <c r="B23">
+        <v>25.34709861160555</v>
+      </c>
+      <c r="C23">
         <v>44.32182271270915</v>
-      </c>
-      <c r="C23">
-        <v>25.34709861160555</v>
       </c>
       <c r="D23">
         <v>2.256224899598394</v>
       </c>
       <c r="E23">
-        <v>26.1225346202266</v>
+        <v>14.93915232899706</v>
       </c>
       <c r="F23">
         <v>58.93831305077633</v>
       </c>
       <c r="G23">
-        <v>14.93915232899706</v>
+        <v>26.1225346202266</v>
       </c>
     </row>
     <row r="24">
@@ -948,22 +948,22 @@
         </is>
       </c>
       <c r="B24">
+        <v>28.53572235187834</v>
+      </c>
+      <c r="C24">
         <v>34.26033275615448</v>
-      </c>
-      <c r="C24">
-        <v>28.53572235187834</v>
       </c>
       <c r="D24">
         <v>2.918827458908324</v>
       </c>
       <c r="E24">
-        <v>21.04494039085839</v>
+        <v>17.52850972521527</v>
       </c>
       <c r="F24">
         <v>61.42654988392634</v>
       </c>
       <c r="G24">
-        <v>17.52850972521527</v>
+        <v>21.04494039085839</v>
       </c>
     </row>
     <row r="25">
@@ -973,22 +973,22 @@
         </is>
       </c>
       <c r="B25">
+        <v>32.11312186059313</v>
+      </c>
+      <c r="C25">
         <v>35.91137411408518</v>
-      </c>
-      <c r="C25">
-        <v>32.11312186059313</v>
       </c>
       <c r="D25">
         <v>2.78463307146963</v>
       </c>
       <c r="E25">
-        <v>21.37270158483148</v>
+        <v>19.11216675539539</v>
       </c>
       <c r="F25">
         <v>59.51513165977313</v>
       </c>
       <c r="G25">
-        <v>19.11216675539539</v>
+        <v>21.37270158483148</v>
       </c>
     </row>
     <row r="26">
@@ -998,22 +998,22 @@
         </is>
       </c>
       <c r="B26">
+        <v>27.37884683409975</v>
+      </c>
+      <c r="C26">
         <v>34.46674920410329</v>
-      </c>
-      <c r="C26">
-        <v>27.37884683409975</v>
       </c>
       <c r="D26">
         <v>2.901347017318794</v>
       </c>
       <c r="E26">
-        <v>21.29606862825451</v>
+        <v>16.91664617654291</v>
       </c>
       <c r="F26">
         <v>61.78728519520258</v>
       </c>
       <c r="G26">
-        <v>16.91664617654291</v>
+        <v>21.29606862825451</v>
       </c>
     </row>
     <row r="27">
@@ -1023,22 +1023,22 @@
         </is>
       </c>
       <c r="B27">
+        <v>29.6664032706909</v>
+      </c>
+      <c r="C27">
         <v>37.54766894561445</v>
-      </c>
-      <c r="C27">
-        <v>29.6664032706909</v>
       </c>
       <c r="D27">
         <v>2.663281178515875</v>
       </c>
       <c r="E27">
-        <v>22.4548499106244</v>
+        <v>17.74157095601077</v>
       </c>
       <c r="F27">
         <v>59.80357913336484</v>
       </c>
       <c r="G27">
-        <v>17.74157095601077</v>
+        <v>22.4548499106244</v>
       </c>
     </row>
     <row r="28">
@@ -1048,22 +1048,22 @@
         </is>
       </c>
       <c r="B28">
+        <v>30.36863220043903</v>
+      </c>
+      <c r="C28">
         <v>38.57391567633033</v>
-      </c>
-      <c r="C28">
-        <v>30.36863220043903</v>
       </c>
       <c r="D28">
         <v>2.592425431711146</v>
       </c>
       <c r="E28">
-        <v>22.83256418298311</v>
+        <v>17.97571575787446</v>
       </c>
       <c r="F28">
         <v>59.19172005914243</v>
       </c>
       <c r="G28">
-        <v>17.97571575787446</v>
+        <v>22.83256418298311</v>
       </c>
     </row>
     <row r="29">
@@ -1073,22 +1073,22 @@
         </is>
       </c>
       <c r="B29">
+        <v>31.22895622895623</v>
+      </c>
+      <c r="C29">
         <v>34.91323491323492</v>
-      </c>
-      <c r="C29">
-        <v>31.22895622895623</v>
       </c>
       <c r="D29">
         <v>2.864243323442136</v>
       </c>
       <c r="E29">
-        <v>21.01406913753459</v>
+        <v>18.79652363693051</v>
       </c>
       <c r="F29">
         <v>60.18940722553489</v>
       </c>
       <c r="G29">
-        <v>18.79652363693051</v>
+        <v>21.01406913753459</v>
       </c>
     </row>
     <row r="30">
@@ -1098,22 +1098,22 @@
         </is>
       </c>
       <c r="B30">
+        <v>29.20156337241765</v>
+      </c>
+      <c r="C30">
         <v>39.13083938209567</v>
-      </c>
-      <c r="C30">
-        <v>29.20156337241765</v>
       </c>
       <c r="D30">
         <v>2.555529131985731</v>
       </c>
       <c r="E30">
-        <v>23.246171706562</v>
+        <v>17.34755929017635</v>
       </c>
       <c r="F30">
         <v>59.40626900326165</v>
       </c>
       <c r="G30">
-        <v>17.34755929017635</v>
+        <v>23.246171706562</v>
       </c>
     </row>
     <row r="31">
@@ -1123,22 +1123,22 @@
         </is>
       </c>
       <c r="B31">
+        <v>30.82370795042576</v>
+      </c>
+      <c r="C31">
         <v>34.86215327544052</v>
-      </c>
-      <c r="C31">
-        <v>30.82370795042576</v>
       </c>
       <c r="D31">
         <v>2.868440145102781</v>
       </c>
       <c r="E31">
+        <v>18.60370445756157</v>
+      </c>
+      <c r="F31">
+        <v>60.35518013433747</v>
+      </c>
+      <c r="G31">
         <v>21.04111540810096</v>
-      </c>
-      <c r="F31">
-        <v>60.35518013433748</v>
-      </c>
-      <c r="G31">
-        <v>18.60370445756157</v>
       </c>
     </row>
   </sheetData>
